--- a/artfynd/A 8635-2025 artfynd.xlsx
+++ b/artfynd/A 8635-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1146,6 +1146,312 @@
           <t>Ecogain</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123703387</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100645</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vingölsbackarna, Vingölsbackarna, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>556507</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6333082</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123703419</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100645</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vingölsbackarna, Vingölsbackarna, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>556502</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6333096</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123704194</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100645</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vingölsbackarna, Vingölsbackarna, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>556537</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6333092</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8635-2025 artfynd.xlsx
+++ b/artfynd/A 8635-2025 artfynd.xlsx
@@ -1152,7 +1152,7 @@
         <v>123703387</v>
       </c>
       <c r="B6" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123703419</v>
+        <v>123704194</v>
       </c>
       <c r="B7" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556502</v>
+        <v>556537</v>
       </c>
       <c r="R7" t="n">
-        <v>6333096</v>
+        <v>6333092</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123704194</v>
+        <v>123703419</v>
       </c>
       <c r="B8" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556537</v>
+        <v>556502</v>
       </c>
       <c r="R8" t="n">
-        <v>6333092</v>
+        <v>6333096</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 8635-2025 artfynd.xlsx
+++ b/artfynd/A 8635-2025 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123703387</v>
+        <v>123704194</v>
       </c>
       <c r="B6" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556507</v>
+        <v>556537</v>
       </c>
       <c r="R6" t="n">
-        <v>6333082</v>
+        <v>6333092</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123704194</v>
+        <v>123703419</v>
       </c>
       <c r="B7" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556537</v>
+        <v>556502</v>
       </c>
       <c r="R7" t="n">
-        <v>6333092</v>
+        <v>6333096</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123703419</v>
+        <v>123703387</v>
       </c>
       <c r="B8" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,16 +1387,20 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Vingölsbackarna, Vingölsbackarna, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556502</v>
+        <v>556507</v>
       </c>
       <c r="R8" t="n">
-        <v>6333096</v>
+        <v>6333082</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1423,12 +1427,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,6 +1441,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 8635-2025 artfynd.xlsx
+++ b/artfynd/A 8635-2025 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123704194</v>
+        <v>123703419</v>
       </c>
       <c r="B6" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556537</v>
+        <v>556502</v>
       </c>
       <c r="R6" t="n">
-        <v>6333092</v>
+        <v>6333096</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123703419</v>
+        <v>123704194</v>
       </c>
       <c r="B7" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556502</v>
+        <v>556537</v>
       </c>
       <c r="R7" t="n">
-        <v>6333096</v>
+        <v>6333092</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1356,7 +1356,7 @@
         <v>123703387</v>
       </c>
       <c r="B8" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 8635-2025 artfynd.xlsx
+++ b/artfynd/A 8635-2025 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123703419</v>
+        <v>123704194</v>
       </c>
       <c r="B6" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556502</v>
+        <v>556537</v>
       </c>
       <c r="R6" t="n">
-        <v>6333096</v>
+        <v>6333092</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123704194</v>
+        <v>123703419</v>
       </c>
       <c r="B7" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556537</v>
+        <v>556502</v>
       </c>
       <c r="R7" t="n">
-        <v>6333092</v>
+        <v>6333096</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1356,7 +1356,7 @@
         <v>123703387</v>
       </c>
       <c r="B8" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 8635-2025 artfynd.xlsx
+++ b/artfynd/A 8635-2025 artfynd.xlsx
@@ -1149,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123704194</v>
+        <v>123703419</v>
       </c>
       <c r="B6" t="n">
         <v>100257</v>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556537</v>
+        <v>556502</v>
       </c>
       <c r="R6" t="n">
-        <v>6333092</v>
+        <v>6333096</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1251,7 +1251,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123703419</v>
+        <v>123704194</v>
       </c>
       <c r="B7" t="n">
         <v>100257</v>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556502</v>
+        <v>556537</v>
       </c>
       <c r="R7" t="n">
-        <v>6333096</v>
+        <v>6333092</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
